--- a/2027赛季雷达兵种项目验收.xlsx
+++ b/2027赛季雷达兵种项目验收.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收记录" sheetId="1" state="visible" r:id="rId1"/>
@@ -1237,7 +1237,7 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>梳理2027规则差异并解析装甲受击信息</t>
+          <t>2027赛季新地图适配</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>完成规则差异梳理，输出装甲受击信息字段清单</t>
+          <t>完成红/蓝视角地图与落点掩码重制</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/1/31</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>可正确解析并落库每发弹丸的击中位置（x，y，命中区域类别）</t>
+          <t>地图、掩码、仿射标定矩阵、盲区预测点位全部换为2027场地，标定点投影与实际场地一致</t>
         </is>
       </c>
       <c r="K4" s="8" t="n"/>
@@ -1291,7 +1291,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2027赛季新地图适配</t>
+          <t>加固区面积A计算与加固指令下发</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/1/31</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>完成红/蓝视角地图与落点掩码重制</t>
+          <t>完成A计算模块并接入裁判系统指令通道</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>2027/1/31</t>
+          <t>2027/2/28</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>地图、掩码、仿射标定矩阵、盲区预测点位全部换为2027场地，标定点投影与实际场地一致</t>
+          <t>正确计算η、σ、ρ、A，对不同数据给出加固策略；加固指令可被裁判系统接受</t>
         </is>
       </c>
       <c r="K5" s="8" t="n"/>
@@ -1345,7 +1345,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>加固区面积A计算与加固指令下发</t>
+          <t>梳理2027规则差异并解析装甲受击信息</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>2027/1/31</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>完成A计算模块并接入裁判系统指令通道</t>
+          <t>完成规则差异梳理，输出装甲受击信息字段清单</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>2027/2/28</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>正确计算η、σ、ρ、A，对不同数据给出加固策略；加固指令可被裁判系统接受</t>
+          <t>可正确解析并落库每发弹丸的击中位置（x，y，命中区域类别）</t>
         </is>
       </c>
       <c r="K6" s="8" t="n"/>
@@ -1399,7 +1399,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>装甲板模型重训</t>
+          <t>解析波接收链路搭建与6位密钥解调</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>视觉</t>
+          <t>硬件</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1427,22 +1427,22 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>2027/2/28</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>完成新装甲板样本采集与模型评估</t>
+          <t>完成2块AD9363板接收链路搭建</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>2027/3/8</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>装甲模块外形/尺寸变化大时完成重训并导出onnx/engine，新装甲板检出率不低于现役模型</t>
+          <t>可接收官方发射源波形，完成6位随机密钥（数字字母组合）重置机制的解调验证</t>
         </is>
       </c>
       <c r="K7" s="8" t="n"/>
@@ -1453,7 +1453,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>解析波接收链路搭建与6位密钥解调</t>
+          <t>自测发射源搭建</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1481,22 +1481,22 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2027/1/31</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>完成2块AD9363板接收链路搭建</t>
+          <t>两块AD9363板并行驱动跑通</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/2/28</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>可接收官方发射源波形，完成6位随机密钥（数字字母组合）重置机制的解调验证</t>
+          <t>以两块AD9363板模拟官方发射源，完成信息波与干扰波的接收端自测</t>
         </is>
       </c>
       <c r="K8" s="8" t="n"/>
@@ -1507,7 +1507,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>自测发射源搭建</t>
+          <t>全链路联调</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>视觉</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -1535,22 +1535,22 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>2027/1/31</t>
+          <t>2027/2/28</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>两块AD9363板并行驱动跑通</t>
+          <t>识别＋加固＋解析波接入同一进程</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>2027/2/28</t>
+          <t>2027/3/8</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>以两块AD9363板模拟官方发射源，完成信息波与干扰波的接收端自测</t>
+          <t>视觉识别＋加固指令＋解析波坐标融合连续运行稳定，P值与易伤上报正常</t>
         </is>
       </c>
       <c r="K9" s="8" t="n"/>
@@ -1561,7 +1561,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>全链路联调</t>
+          <t>四位数SDR采购与参数标定</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>视觉</t>
+          <t>硬件</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1587,24 +1587,16 @@
       <c r="F10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>2027/2/28</t>
-        </is>
-      </c>
+      <c r="G10" s="8" t="n"/>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>识别＋加固＋解析波接入同一进程</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>2027/3/8</t>
-        </is>
-      </c>
+          <t>官方发布解析波参数后启动采购</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>视觉识别＋加固指令＋解析波坐标融合连续运行稳定，P值与易伤上报正常</t>
+          <t>采购AD9361板卡，按官方干扰波三级难度参数完成频点、带宽、功率标定</t>
         </is>
       </c>
       <c r="K10" s="8" t="n"/>
@@ -1615,7 +1607,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>四位数SDR采购与参数标定</t>
+          <t>装甲板模型重训</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -1630,7 +1622,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>视觉</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1641,16 +1633,24 @@
       <c r="F11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="8" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>2027/2/28</t>
+        </is>
+      </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>官方发布解析波参数后启动采购</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr"/>
+          <t>完成新装甲板样本采集与模型评估</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>2027/3/8</t>
+        </is>
+      </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>采购AD9361板卡，按官方干扰波三级难度参数完成频点、带宽、功率标定</t>
+          <t>装甲模块外形/尺寸变化大时完成重训并导出onnx/engine，新装甲板检出率不低于现役模型</t>
         </is>
       </c>
       <c r="K11" s="8" t="n"/>

--- a/2027赛季雷达兵种项目验收.xlsx
+++ b/2027赛季雷达兵种项目验收.xlsx
@@ -145,14 +145,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -521,36 +521,36 @@
   <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="30" customWidth="1" style="7" min="1" max="1"/>
-    <col width="12" customWidth="1" style="7" min="2" max="3"/>
-    <col width="10" customWidth="1" style="7" min="4" max="4"/>
-    <col width="12" customWidth="1" style="7" min="5" max="5"/>
-    <col width="14" customWidth="1" style="7" min="6" max="6"/>
-    <col width="16" customWidth="1" style="7" min="7" max="8"/>
-    <col width="18" customWidth="1" style="7" min="9" max="9"/>
-    <col width="34" customWidth="1" style="7" min="10" max="10"/>
-    <col width="12" customWidth="1" style="7" min="11" max="11"/>
-    <col width="28" customWidth="1" style="7" min="12" max="12"/>
-    <col width="10" customWidth="1" style="7" min="13" max="13"/>
-    <col width="12" customWidth="1" style="7" min="14" max="14"/>
-    <col width="10" customWidth="1" style="7" min="15" max="16"/>
+    <col width="30" customWidth="1" style="8" min="1" max="1"/>
+    <col width="12" customWidth="1" style="8" min="2" max="3"/>
+    <col width="10" customWidth="1" style="8" min="4" max="4"/>
+    <col width="12" customWidth="1" style="8" min="5" max="5"/>
+    <col width="14" customWidth="1" style="8" min="6" max="6"/>
+    <col width="16" customWidth="1" style="8" min="7" max="8"/>
+    <col width="18" customWidth="1" style="8" min="9" max="9"/>
+    <col width="34" customWidth="1" style="8" min="10" max="10"/>
+    <col width="12" customWidth="1" style="8" min="11" max="11"/>
+    <col width="28" customWidth="1" style="8" min="12" max="12"/>
+    <col width="10" customWidth="1" style="8" min="13" max="13"/>
+    <col width="12" customWidth="1" style="8" min="14" max="14"/>
+    <col width="10" customWidth="1" style="8" min="15" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1" s="7">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="21.75" customHeight="1" s="8">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>项目验收记录表（对应多维表格「进度管理 · 任务信息表」录入）</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" s="7">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2" ht="28" customHeight="1" s="8">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>蓝底列＝录入多维表格的内容；红底列＝验收过程记录，不录入Base（验收意见由组长写入备注）。带*为必填。日期格式 yyyy/M/d。灰色斜体为示例，填写时覆盖。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="7">
+    <row r="3" ht="30" customHeight="1" s="8">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>任务简述</t>
@@ -622,7 +622,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="43.5" customHeight="1" s="7">
+    <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>2027赛季新地图适配</t>
@@ -653,7 +653,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2027/1/15</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/1/31</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -676,7 +676,7 @@
       <c r="M4" s="5" t="n"/>
       <c r="N4" s="5" t="n"/>
     </row>
-    <row r="5" ht="43.5" customHeight="1" s="7">
+    <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>加固区面积A计算与加固指令下发</t>
@@ -707,17 +707,17 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
+          <t>2027/2/14</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>完成A计算模块,能得出各种情况下的加固策略</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>2027/1/31</t>
+          <t>2027/2/28</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -730,7 +730,7 @@
       <c r="M5" s="5" t="n"/>
       <c r="N5" s="5" t="n"/>
     </row>
-    <row r="6" ht="43.5" customHeight="1" s="7">
+    <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>梳理2027规则差异并解析装甲受击信息</t>
@@ -761,7 +761,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>2027/1/31</t>
+          <t>2026/12/1</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>2027/2/28</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -784,7 +784,7 @@
       <c r="M6" s="5" t="n"/>
       <c r="N6" s="5" t="n"/>
     </row>
-    <row r="7" ht="43.5" customHeight="1" s="7">
+    <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>解析波接收链路搭建与6位密钥解调</t>
@@ -815,7 +815,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>2027/2/28</t>
+          <t>2026/12/1</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>2027/3/8</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -838,10 +838,10 @@
       <c r="M7" s="5" t="n"/>
       <c r="N7" s="5" t="n"/>
     </row>
-    <row r="8" ht="29" customHeight="1" s="7">
+    <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>自测发射源搭建</t>
+          <t>全链路联调</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>视觉</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -869,22 +869,22 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2027/3/4</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>两块AD9363板并行驱动跑通</t>
+          <t>识别＋加固＋解析波接入同一进程</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/3/8</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>以两块AD9363板模拟官方发射源，完成信息波与干扰波的接收端自测</t>
+          <t>视觉识别＋加固指令＋解析波坐标融合连续运行稳定，P值与易伤上报正常</t>
         </is>
       </c>
       <c r="K8" s="5" t="n"/>
@@ -892,10 +892,10 @@
       <c r="M8" s="5" t="n"/>
       <c r="N8" s="5" t="n"/>
     </row>
-    <row r="9" ht="43.5" customHeight="1" s="7">
+    <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>全链路联调</t>
+          <t>四位数SDR采购与参数标定</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>视觉</t>
+          <t>硬件</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -921,24 +921,20 @@
       <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>2027/1/31</t>
-        </is>
-      </c>
+      <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>识别＋加固＋解析波接入同一进程</t>
+          <t>官方发布解析波参数后启动采购</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>2027/2/28</t>
+          <t>官方参数发布后</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>视觉识别＋加固指令＋解析波坐标融合连续运行稳定，P值与易伤上报正常</t>
+          <t>采购AD9361板卡，按官方干扰波三级难度参数完成频点、带宽、功率标定</t>
         </is>
       </c>
       <c r="K9" s="5" t="n"/>
@@ -946,10 +942,10 @@
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="5" t="n"/>
     </row>
-    <row r="10" ht="43.5" customHeight="1" s="7">
+    <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>四位数SDR采购与参数标定</t>
+          <t>装甲板模型重训</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -964,7 +960,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>视觉</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -977,12 +973,12 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>2027/2/28</t>
+          <t>2027/3/4</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>官方发布解析波参数后启动采购</t>
+          <t>完成新装甲板样本采集与模型评估</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -992,7 +988,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>采购AD9361板卡，按官方干扰波三级难度参数完成频点、带宽、功率标定</t>
+          <t>装甲模块外形/尺寸变化大时完成重训并导出onnx/engine，新装甲板检出率不低于现役模型</t>
         </is>
       </c>
       <c r="K10" s="5" t="n"/>
@@ -1000,53 +996,23 @@
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="n"/>
     </row>
-    <row r="11" ht="43.5" customHeight="1" s="7">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>装甲板模型重训</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>待开始</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>雷达</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>视觉</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>苏展鸣</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0</v>
-      </c>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>完成新装甲板样本采集与模型评估</t>
-        </is>
-      </c>
+      <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>装甲模块外形/尺寸变化大时完成重训并导出onnx/engine，新装甲板检出率不低于现役模型</t>
-        </is>
-      </c>
+      <c r="J11" s="5" t="n"/>
       <c r="K11" s="5" t="n"/>
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="5" t="n"/>
       <c r="N11" s="5" t="n"/>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="7">
+    <row r="12" ht="16.5" customHeight="1" s="8">
       <c r="A12" s="2" t="n"/>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
@@ -1062,7 +1028,7 @@
       <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="n"/>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="7">
+    <row r="13" ht="16.5" customHeight="1" s="8">
       <c r="A13" s="2" t="n"/>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
@@ -1078,7 +1044,7 @@
       <c r="M13" s="2" t="n"/>
       <c r="N13" s="2" t="n"/>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="7">
+    <row r="14" ht="16.5" customHeight="1" s="8">
       <c r="A14" s="2" t="n"/>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
@@ -1094,7 +1060,7 @@
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="7">
+    <row r="15" ht="16.5" customHeight="1" s="8">
       <c r="A15" s="2" t="n"/>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
@@ -1110,7 +1076,7 @@
       <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="n"/>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="7">
+    <row r="16" ht="16.5" customHeight="1" s="8">
       <c r="A16" s="2" t="n"/>
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="n"/>
@@ -1126,7 +1092,7 @@
       <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="7">
+    <row r="17" ht="16.5" customHeight="1" s="8">
       <c r="A17" s="2" t="n"/>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
@@ -1142,7 +1108,7 @@
       <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="7">
+    <row r="18" ht="16.5" customHeight="1" s="8">
       <c r="A18" s="2" t="n"/>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
@@ -1158,7 +1124,7 @@
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="7">
+    <row r="19" ht="16.5" customHeight="1" s="8">
       <c r="A19" s="2" t="n"/>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
@@ -1174,7 +1140,7 @@
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="7">
+    <row r="20" ht="16.5" customHeight="1" s="8">
       <c r="A20" s="2" t="n"/>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
@@ -1190,7 +1156,7 @@
       <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
     </row>
-    <row r="21" ht="16.5" customHeight="1" s="7">
+    <row r="21" ht="16.5" customHeight="1" s="8">
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
@@ -1206,7 +1172,7 @@
       <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="n"/>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="7">
+    <row r="22" ht="16.5" customHeight="1" s="8">
       <c r="A22" s="2" t="n"/>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
@@ -1222,7 +1188,7 @@
       <c r="M22" s="2" t="n"/>
       <c r="N22" s="2" t="n"/>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="7">
+    <row r="23" ht="16.5" customHeight="1" s="8">
       <c r="A23" s="2" t="n"/>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
@@ -1238,7 +1204,7 @@
       <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="n"/>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="7">
+    <row r="24" ht="16.5" customHeight="1" s="8">
       <c r="A24" s="2" t="n"/>
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="n"/>
@@ -1254,7 +1220,7 @@
       <c r="M24" s="2" t="n"/>
       <c r="N24" s="2" t="n"/>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="7">
+    <row r="25" ht="16.5" customHeight="1" s="8">
       <c r="A25" s="2" t="n"/>
       <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="n"/>
@@ -1270,7 +1236,7 @@
       <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="n"/>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="7">
+    <row r="26" ht="16.5" customHeight="1" s="8">
       <c r="A26" s="2" t="n"/>
       <c r="B26" s="2" t="n"/>
       <c r="C26" s="2" t="n"/>
@@ -1286,7 +1252,7 @@
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="7">
+    <row r="27" ht="16.5" customHeight="1" s="8">
       <c r="A27" s="2" t="n"/>
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="n"/>
@@ -1302,7 +1268,7 @@
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="7">
+    <row r="28" ht="16.5" customHeight="1" s="8">
       <c r="A28" s="2" t="n"/>
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="n"/>
@@ -1318,7 +1284,7 @@
       <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="7">
+    <row r="29" ht="16.5" customHeight="1" s="8">
       <c r="A29" s="2" t="n"/>
       <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="n"/>
@@ -1334,7 +1300,7 @@
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="7">
+    <row r="30" ht="16.5" customHeight="1" s="8">
       <c r="A30" s="2" t="n"/>
       <c r="B30" s="2" t="n"/>
       <c r="C30" s="2" t="n"/>
@@ -1350,7 +1316,7 @@
       <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
     </row>
-    <row r="31" ht="16.5" customHeight="1" s="7">
+    <row r="31" ht="16.5" customHeight="1" s="8">
       <c r="A31" s="2" t="n"/>
       <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="n"/>
@@ -1366,7 +1332,7 @@
       <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="7">
+    <row r="32" ht="16.5" customHeight="1" s="8">
       <c r="A32" s="2" t="n"/>
       <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="n"/>
@@ -1382,7 +1348,7 @@
       <c r="M32" s="2" t="n"/>
       <c r="N32" s="2" t="n"/>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="7">
+    <row r="33" ht="16.5" customHeight="1" s="8">
       <c r="A33" s="2" t="n"/>
       <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="n"/>
@@ -1398,7 +1364,7 @@
       <c r="M33" s="2" t="n"/>
       <c r="N33" s="2" t="n"/>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="7">
+    <row r="34" ht="16.5" customHeight="1" s="8">
       <c r="A34" s="2" t="n"/>
       <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
@@ -1443,20 +1409,20 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="20" customWidth="1" style="7" min="1" max="1"/>
-    <col width="24" customWidth="1" style="7" min="2" max="2"/>
-    <col width="62" customWidth="1" style="7" min="3" max="3"/>
-    <col width="2" customWidth="1" style="7" min="4" max="4"/>
+    <col width="20" customWidth="1" style="8" min="1" max="1"/>
+    <col width="24" customWidth="1" style="8" min="2" max="2"/>
+    <col width="62" customWidth="1" style="8" min="3" max="3"/>
+    <col width="2" customWidth="1" style="8" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1" s="7">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="21.75" customHeight="1" s="8">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>字段对照与填写规则（依据《进度验收规范 V1.0》）</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" s="7">
+    <row r="3" ht="22" customHeight="1" s="8">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>模板列</t>
@@ -1473,7 +1439,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="7">
+    <row r="4" ht="16.5" customHeight="1" s="8">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>任务描述</t>
@@ -1490,7 +1456,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="33" customHeight="1" s="7">
+    <row r="5" ht="33" customHeight="1" s="8">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>任务状态</t>
@@ -1507,7 +1473,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="7">
+    <row r="6" ht="16.5" customHeight="1" s="8">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>所属兵种</t>
@@ -1524,7 +1490,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1" s="7">
+    <row r="7" ht="16.5" customHeight="1" s="8">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>技术组</t>
@@ -1541,7 +1507,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="7">
+    <row r="8" ht="16.5" customHeight="1" s="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>负责人</t>
@@ -1558,7 +1524,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="7">
+    <row r="9" ht="16.5" customHeight="1" s="8">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>完成进度百分比</t>
@@ -1575,7 +1541,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="7">
+    <row r="10" ht="16.5" customHeight="1" s="8">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>中期节点</t>
@@ -1592,7 +1558,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="33" customHeight="1" s="7">
+    <row r="11" ht="33" customHeight="1" s="8">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>计划完成时间</t>
@@ -1609,7 +1575,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="7">
+    <row r="12" ht="16.5" customHeight="1" s="8">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>父任务</t>
@@ -1626,7 +1592,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="7">
+    <row r="13" ht="16.5" customHeight="1" s="8">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>交付物/验收标准</t>
@@ -1643,7 +1609,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1" s="7">
+    <row r="14" ht="16.5" customHeight="1" s="8">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>验收结论</t>
@@ -1660,7 +1626,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" s="7">
+    <row r="15" ht="16.5" customHeight="1" s="8">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>验收意见</t>
@@ -1677,7 +1643,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="7">
+    <row r="16" ht="16.5" customHeight="1" s="8">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>验收人/验收日期</t>

--- a/2027赛季雷达兵种项目验收.xlsx
+++ b/2027赛季雷达兵种项目验收.xlsx
@@ -622,10 +622,10 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="43.5" customHeight="1" s="8">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>2027赛季新地图适配</t>
+          <t>梳理2027规则差异并解析装甲受击信息</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -653,22 +653,22 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>2027/1/15</t>
+          <t>2026/12/1</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>完成红/蓝视角地图与落点掩码重制</t>
+          <t>完成规则差异梳理，输出装甲受击信息字段清单</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>2027/1/31</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>地图、掩码、仿射标定矩阵、盲区预测点位全部换为2027场地，标定点投影与实际场地一致</t>
+          <t>可正确解析并落库每发弹丸的击中位置（x，y，命中区域类别）</t>
         </is>
       </c>
       <c r="K4" s="5" t="n"/>
@@ -676,10 +676,10 @@
       <c r="M4" s="5" t="n"/>
       <c r="N4" s="5" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="43.5" customHeight="1" s="8">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>加固区面积A计算与加固指令下发</t>
+          <t>解析波接收链路搭建与6位密钥解调</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -707,22 +707,22 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>2027/2/14</t>
+          <t>2026/12/1</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>完成A计算模块,能得出各种情况下的加固策略</t>
+          <t>完成2块AD9363板接收链路搭建</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>2027/2/28</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>正确计算η、σ、ρ、A，对不同数据给出加固策略；加固指令可被裁判系统接受</t>
+          <t>可接收官方发射源波形，完成6位随机密钥（数字字母组合）重置机制的解调验证</t>
         </is>
       </c>
       <c r="K5" s="5" t="n"/>
@@ -730,10 +730,10 @@
       <c r="M5" s="5" t="n"/>
       <c r="N5" s="5" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="43.5" customHeight="1" s="8">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>梳理2027规则差异并解析装甲受击信息</t>
+          <t>2027赛季新地图适配</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -761,22 +761,22 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>2026/12/1</t>
+          <t>2027/1/15</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>完成规则差异梳理，输出装甲受击信息字段清单</t>
+          <t>完成红/蓝视角地图与落点掩码重制</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/1/31</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>可正确解析并落库每发弹丸的击中位置（x，y，命中区域类别）</t>
+          <t>地图、掩码、仿射标定矩阵、盲区预测点位全部换为2027场地，标定点投影与实际场地一致</t>
         </is>
       </c>
       <c r="K6" s="5" t="n"/>
@@ -784,10 +784,10 @@
       <c r="M6" s="5" t="n"/>
       <c r="N6" s="5" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="43.5" customHeight="1" s="8">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>解析波接收链路搭建与6位密钥解调</t>
+          <t>加固区面积A计算与加固指令下发</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>视觉</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>2026/12/1</t>
+          <t>2027/2/14</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>完成2块AD9363板接收链路搭建</t>
+          <t>完成A计算模块,能得出各种情况下的加固策略</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/2/28</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>可接收官方发射源波形，完成6位随机密钥（数字字母组合）重置机制的解调验证</t>
+          <t>正确计算η、σ、ρ、A，对不同数据给出加固策略；加固指令可被裁判系统接受</t>
         </is>
       </c>
       <c r="K7" s="5" t="n"/>
@@ -838,7 +838,7 @@
       <c r="M7" s="5" t="n"/>
       <c r="N7" s="5" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="43.5" customHeight="1" s="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>全链路联调</t>
@@ -892,10 +892,10 @@
       <c r="M8" s="5" t="n"/>
       <c r="N8" s="5" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="43.5" customHeight="1" s="8">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>四位数SDR采购与参数标定</t>
+          <t>装甲板模型重训</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>硬件</t>
+          <t>视觉</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -921,20 +921,24 @@
       <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>2027/3/4</t>
+        </is>
+      </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>官方发布解析波参数后启动采购</t>
+          <t>完成新装甲板样本采集与模型评估</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>官方参数发布后</t>
+          <t>2027/3/8</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>采购AD9361板卡，按官方干扰波三级难度参数完成频点、带宽、功率标定</t>
+          <t>装甲模块外形/尺寸变化大时完成重训并导出onnx/engine，新装甲板检出率不低于现役模型</t>
         </is>
       </c>
       <c r="K9" s="5" t="n"/>
@@ -942,10 +946,10 @@
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="5" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="43.5" customHeight="1" s="8">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>装甲板模型重训</t>
+          <t>四位数SDR采购与参数标定</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -971,24 +975,20 @@
       <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>2027/3/4</t>
-        </is>
-      </c>
+      <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>完成新装甲板样本采集与模型评估</t>
+          <t>官方发布解析波参数后启动采购</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>2027/3/8</t>
+          <t>官方参数发布后</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>装甲模块外形/尺寸变化大时完成重训并导出onnx/engine，新装甲板检出率不低于现役模型</t>
+          <t>采购AD9361板卡，按官方干扰波三级难度参数完成频点、带宽、功率标定</t>
         </is>
       </c>
       <c r="K10" s="5" t="n"/>
@@ -996,7 +996,7 @@
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="16.5" customHeight="1" s="8">
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>

--- a/2027赛季雷达兵种项目验收.xlsx
+++ b/2027赛季雷达兵种项目验收.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="新細明體"/>
       <charset val="134"/>
@@ -63,6 +63,10 @@
       <charset val="134"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -84,7 +88,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -122,13 +126,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -153,6 +163,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -622,411 +635,487 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="43.5" customHeight="1" s="8">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>梳理2027规则差异并解析装甲受击信息</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>适配2027新地图（地图、掩码、标定矩阵、盲区点位）</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>待开始</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>雷达</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>视觉</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>苏展鸣</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>2026/12/1</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>完成红/蓝视角地图与落点掩码重制</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>地图、掩码、仿射标定矩阵、盲区预测点位全部换为2027场地，标定点投影与实际场地一致</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>加固区面积A计算与加固指令联调</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>待开始</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>雷达</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>视觉</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>苏展鸣</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/1</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>完成A计算模块,能得出各种情况下的加固策略</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>正确计算η、σ、ρ、A，对不同数据给出加固策略；加固指令可被裁判系统接受</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>搭建自测发射源完成接收端自测</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>待开始</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>雷达</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>视觉</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>苏展鸣</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/1</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>两块AD9363板并行驱动跑通</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>以两块AD9363板模拟官方发射源，完成信息波与干扰波的接收端自测</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>梳理2027规则差异、解析装甲受击信息</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>待开始</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>雷达</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>视觉</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>苏展鸣</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>2027/1/29</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>完成规则差异梳理，输出装甲受击信息字段清单</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>2026/12/31</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>2027/2/28</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>可正确解析并落库每发弹丸的击中位置（x，y，命中区域类别）</t>
         </is>
       </c>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="43.5" customHeight="1" s="8">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>解析波接收链路搭建与6位密钥解调</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>SDR采购与接收链路搭建</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>待开始</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>雷达</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>视觉</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>苏展鸣</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>2026/12/1</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>2027/1/29</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>完成2块AD9363板接收链路搭建</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>2026/12/31</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>可接收官方发射源波形，完成6位随机密钥（数字字母组合）重置机制的解调验证</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="43.5" customHeight="1" s="8">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>2027赛季新地图适配</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>2027/2/28</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>接收链路搭建完成，可接收官方发射源波形</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>干扰波三级难度接收与6位密钥解调验证</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>待开始</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>雷达</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>视觉</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>苏展鸣</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>2027/1/15</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>完成红/蓝视角地图与落点掩码重制</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>2027/1/31</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>地图、掩码、仿射标定矩阵、盲区预测点位全部换为2027场地，标定点投影与实际场地一致</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="43.5" customHeight="1" s="8">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>加固区面积A计算与加固指令下发</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>2027/1/29</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>三级难度干扰波接收跑通</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>2027/2/28</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>完成6位随机密钥（数字字母组合）重置机制的解调验证</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>装甲板模型评估与重训</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>待开始</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>雷达</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>视觉</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>苏展鸣</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F10" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>2027/2/14</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>完成A计算模块,能得出各种情况下的加固策略</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>2027/2/28</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>正确计算η、σ、ρ、A，对不同数据给出加固策略；加固指令可被裁判系统接受</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="43.5" customHeight="1" s="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>全链路联调</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>2027/3/15</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>完成新装甲板样本采集与模型评估</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>2027/3/31</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>装甲模块外形/尺寸变化大时完成重训并导出onnx/engine，新装甲板检出率不低于现役模型</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>全链路联调（识别＋加固＋解析波）</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>待开始</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>雷达</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>视觉</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>苏展鸣</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F11" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>2027/3/4</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>2027/3/15</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>识别＋加固＋解析波接入同一进程</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>2027/3/8</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>2027/3/31</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>视觉识别＋加固指令＋解析波坐标融合连续运行稳定，P值与易伤上报正常</t>
         </is>
       </c>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="43.5" customHeight="1" s="8">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>装甲板模型重训</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>采购四位数SDR（AD9361）并标定参数</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>待开始</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>雷达</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>视觉</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>苏展鸣</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F12" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>2027/3/4</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>完成新装甲板样本采集与模型评估</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>2027/3/8</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>装甲模块外形/尺寸变化大时完成重训并导出onnx/engine，新装甲板检出率不低于现役模型</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="43.5" customHeight="1" s="8">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>四位数SDR采购与参数标定</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>待开始</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>雷达</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>视觉</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>苏展鸣</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr"/>
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>官方发布解析波参数后启动采购</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>官方参数发布后</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>采购AD9361板卡，按官方干扰波三级难度参数完成频点、带宽、功率标定</t>
         </is>
       </c>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" s="8">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" s="8">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="8">
       <c r="A13" s="2" t="n"/>

--- a/2027赛季雷达兵种项目验收.xlsx
+++ b/2027赛季雷达兵种项目验收.xlsx
@@ -746,7 +746,7 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>搭建自测发射源完成接收端自测</t>
+          <t>梳理2027规则差异、解析装甲受击信息</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -774,22 +774,22 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>2026/12/1</t>
+          <t>2027/1/29</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>两块AD9363板并行驱动跑通</t>
+          <t>完成规则差异梳理，输出装甲受击信息字段清单</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/2/28</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>以两块AD9363板模拟官方发射源，完成信息波与干扰波的接收端自测</t>
+          <t>可正确解析并落库每发弹丸的击中位置（x，y，命中区域类别）</t>
         </is>
       </c>
       <c r="K6" s="10" t="n"/>
@@ -800,7 +800,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>梳理2027规则差异、解析装甲受击信息</t>
+          <t>SDR采购与接收链路搭建</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>完成规则差异梳理，输出装甲受击信息字段清单</t>
+          <t>完成2块AD9363板接收链路搭建</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>可正确解析并落库每发弹丸的击中位置（x，y，命中区域类别）</t>
+          <t>接收链路搭建完成，可接收官方发射源波形</t>
         </is>
       </c>
       <c r="K7" s="10" t="n"/>
@@ -854,7 +854,7 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>SDR采购与接收链路搭建</t>
+          <t>搭建自测发射源完成接收端自测</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>完成2块AD9363板接收链路搭建</t>
+          <t>两块AD9363板并行驱动跑通</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>接收链路搭建完成，可接收官方发射源波形</t>
+          <t>以两块AD9363板模拟官方发射源，完成信息波与干扰波的接收端自测</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -1096,7 +1096,7 @@
       <c r="F12" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="10" t="inlineStr"/>
+      <c r="G12" s="10" t="n"/>
       <c r="H12" s="10" t="inlineStr">
         <is>
           <t>官方发布解析波参数后启动采购</t>
